--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R284da6cc428f4efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rab929aa6b9064508"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R707619b9ad384711"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R8b78c0a1de70498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R43196bb294534275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R71f8a64374034ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc96582e2db84424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rfbfba7a0db0f4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R58ba974b500f4072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R9d1aaf0e2a3349a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -655,7 +655,7 @@
     </x:row>
     <x:row r="7" ht="78" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>output/ab_attribution_review.db,output/rebuild_ab_attribution.sql,output/reports/cohort_metrics.csv,output/reports/sample_contamination.csv,output/reports/attribution_window.csv</x:v>
@@ -664,7 +664,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>交付物清单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -866,7 +866,7 @@
         <x:v>允许范围</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>不变条件</x:v>
+        <x:v>仍需满足</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" customHeight="1">
